--- a/experiments/results/resnet18/CIFAR-10/baseline/energy/adaptive/max/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/baseline/energy/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -519,6 +519,55 @@
       <c r="O3" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>96.47</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
